--- a/Normalisasi_SalesDB_Muhammad Fariz.xlsx
+++ b/Normalisasi_SalesDB_Muhammad Fariz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Maganghub\Bootcamp\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D262E7-6C58-4441-BB2F-322AF14B6E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F608BC-C78E-4ACB-9E5D-D3BB61E59232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -47,8 +47,32 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{DEF09F52-0625-4ACE-9821-9B4DB9D1CC17}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="127">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -420,9 +444,6 @@
     <t>Aksesoris Komputer</t>
   </si>
   <si>
-    <t>Saya menghapus kolom Total Faktur karena total bisa dihitung melalui perhitungan qty dengan harga satuan</t>
-  </si>
-  <si>
     <t>P004</t>
   </si>
   <si>
@@ -453,11 +474,27 @@
     <t>Keyboard Mekanik</t>
   </si>
   <si>
-    <t>No Faktur, Kode Pelanggan</t>
-  </si>
-  <si>
-    <t>No Faktur -&gt; Tanggal, Qty
-Kode Pelanggan -&gt; Nama Pelanggan, Email, Kota</t>
+    <t>No Faktur, Kode Produk</t>
+  </si>
+  <si>
+    <t>No Faktur -&gt; Tanggal, Kode Pelanggan (partial)
+Kode Produk -&gt; Nama Produk, Kode Kategori (partial)</t>
+  </si>
+  <si>
+    <t>Tabel Faktur</t>
+  </si>
+  <si>
+    <t>Tabel Produk</t>
+  </si>
+  <si>
+    <t>Tabel Detail Faktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(No Faktur, Kode Produk) -&gt; Qty, Harga Satuan (full)
+No Faktur -&gt; Tanggal, Kode Pelanggan 
+Kode Pelanggan -&gt; Nama Pelanggan, Email, Kota 
+Kode Produk -&gt; Nama Produk, Kode Kategori 
+Kode Kategori -&gt; Nama Kategori </t>
   </si>
 </sst>
 </file>
@@ -465,9 +502,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,8 +568,35 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -562,6 +626,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -603,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -621,7 +697,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -631,17 +707,33 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1396,12 +1488,12 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1417,12 +1509,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="21.5703125" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
@@ -1432,65 +1524,64 @@
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
     <col min="10" max="10" width="22.28515625" customWidth="1"/>
     <col min="12" max="12" width="16.7109375" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>123</v>
+      <c r="B7" s="19" t="s">
+        <v>122</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="16"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -1508,7 +1599,7 @@
       <c r="F11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="23" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="11" t="s">
@@ -1526,15 +1617,18 @@
       <c r="L11" s="11" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="M11" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="13">
         <v>46266</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="12" t="s">
@@ -1546,11 +1640,11 @@
       <c r="F12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="H12" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>119</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>64</v>
@@ -1564,15 +1658,18 @@
       <c r="L12" s="14">
         <v>1850000</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="M12" s="14">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="13">
         <v>46266</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="12" t="s">
@@ -1584,7 +1681,7 @@
       <c r="F13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="25" t="s">
         <v>105</v>
       </c>
       <c r="H13" s="12" t="s">
@@ -1602,9 +1699,12 @@
       <c r="L13" s="14">
         <v>150000</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="M13" s="14">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="13">
@@ -1622,11 +1722,11 @@
       <c r="F14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H14" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="I14" s="12" t="s">
         <v>109</v>
@@ -1640,9 +1740,12 @@
       <c r="L14" s="14">
         <v>750000</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="M14" s="14">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="13">
@@ -1660,7 +1763,7 @@
       <c r="F15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="25" t="s">
         <v>105</v>
       </c>
       <c r="H15" s="12" t="s">
@@ -1678,9 +1781,12 @@
       <c r="L15" s="14">
         <v>150000</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="M15" s="14">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="13">
@@ -1698,7 +1804,7 @@
       <c r="F16" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="25" t="s">
         <v>62</v>
       </c>
       <c r="H16" s="12" t="s">
@@ -1716,9 +1822,12 @@
       <c r="L16" s="14">
         <v>350000</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="M16" s="14">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
         <v>68</v>
       </c>
       <c r="B17" s="13">
@@ -1736,17 +1845,17 @@
       <c r="F17" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H17" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="I17" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="J17" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>115</v>
       </c>
       <c r="K17" s="12">
         <v>10</v>
@@ -1754,9 +1863,12 @@
       <c r="L17" s="14">
         <v>25000</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="M17" s="14">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="13">
@@ -1774,17 +1886,17 @@
       <c r="F18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="I18" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="J18" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>115</v>
       </c>
       <c r="K18" s="12">
         <v>2</v>
@@ -1792,9 +1904,12 @@
       <c r="L18" s="14">
         <v>48000</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="M18" s="14">
+        <v>346000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24" t="s">
         <v>75</v>
       </c>
       <c r="B19" s="13">
@@ -1812,7 +1927,7 @@
       <c r="F19" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="25" t="s">
         <v>62</v>
       </c>
       <c r="H19" s="12" t="s">
@@ -1830,9 +1945,12 @@
       <c r="L19" s="14">
         <v>375000</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="M19" s="14">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="24" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="13">
@@ -1850,17 +1968,17 @@
       <c r="F20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H20" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="I20" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>115</v>
       </c>
       <c r="K20" s="12">
         <v>5</v>
@@ -1868,9 +1986,12 @@
       <c r="L20" s="14">
         <v>25000</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="M20" s="14">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24" t="s">
         <v>75</v>
       </c>
       <c r="B21" s="13">
@@ -1888,17 +2009,17 @@
       <c r="F21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="I21" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="J21" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>115</v>
       </c>
       <c r="K21" s="12">
         <v>1</v>
@@ -1906,9 +2027,12 @@
       <c r="L21" s="14">
         <v>48000</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="M21" s="14">
+        <v>548000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="13">
@@ -1926,7 +2050,7 @@
       <c r="F22" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="25" t="s">
         <v>104</v>
       </c>
       <c r="H22" s="12" t="s">
@@ -1944,9 +2068,12 @@
       <c r="L22" s="14">
         <v>1850000</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="M22" s="14">
+        <v>4450000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="13">
@@ -1964,39 +2091,45 @@
       <c r="F23" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="H23" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="I23" s="21" t="s">
+      <c r="I23" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="J23" s="21" t="s">
+      <c r="J23" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="K23" s="21">
+      <c r="K23" s="20">
         <v>1</v>
       </c>
-      <c r="L23" s="22">
+      <c r="L23" s="21">
         <v>750000</v>
+      </c>
+      <c r="M23" s="14">
+        <v>4450000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
@@ -2023,16 +2156,20 @@
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="16" t="s">
+        <v>121</v>
+      </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
@@ -2049,9 +2186,358 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+      <c r="A11" s="27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C31" s="12">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="12">
+        <v>2</v>
+      </c>
+      <c r="D32" s="14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="12">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="12">
+        <v>1</v>
+      </c>
+      <c r="D34" s="14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="12">
+        <v>3</v>
+      </c>
+      <c r="D35" s="14">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="12">
+        <v>10</v>
+      </c>
+      <c r="D36" s="14">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="12">
+        <v>2</v>
+      </c>
+      <c r="D37" s="14">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="12">
+        <v>1</v>
+      </c>
+      <c r="D38" s="14">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="12">
+        <v>5</v>
+      </c>
+      <c r="D39" s="14">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="12">
+        <v>1</v>
+      </c>
+      <c r="D40" s="14">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="12">
+        <v>2</v>
+      </c>
+      <c r="D41" s="14">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="20">
+        <v>1</v>
+      </c>
+      <c r="D42" s="21">
+        <v>750000</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Normalisasi_SalesDB_Muhammad Fariz.xlsx
+++ b/Normalisasi_SalesDB_Muhammad Fariz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Maganghub\Bootcamp\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F608BC-C78E-4ACB-9E5D-D3BB61E59232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0769C4A1-1646-44DB-A27E-7F50B141E337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="140">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -495,6 +495,45 @@
 Kode Pelanggan -&gt; Nama Pelanggan, Email, Kota 
 Kode Produk -&gt; Nama Produk, Kode Kategori 
 Kode Kategori -&gt; Nama Kategori </t>
+  </si>
+  <si>
+    <t>No Faktur (PK, FK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK, FK)</t>
+  </si>
+  <si>
+    <t>Tabel Pelanggan</t>
+  </si>
+  <si>
+    <t>Tabel Kategori</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan, Kode Kategori</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan -&gt; Nama Pelanggan, Email, Kota</t>
+  </si>
+  <si>
+    <t>Kode Kategori -&gt; Nama Kategori</t>
+  </si>
+  <si>
+    <t>Kode Kategori (PK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (FK)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (FK)</t>
+  </si>
+  <si>
+    <t>No Faktur (PK)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (PK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK)</t>
   </si>
 </sst>
 </file>
@@ -504,7 +543,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,8 +634,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -640,6 +686,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -679,7 +749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -706,7 +776,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -733,7 +802,37 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1562,7 +1661,7 @@
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>122</v>
       </c>
       <c r="C7" s="17" t="s">
@@ -1581,7 +1680,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -1599,7 +1698,7 @@
       <c r="F11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="22" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="11" t="s">
@@ -1622,13 +1721,13 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>35</v>
       </c>
       <c r="B12" s="13">
         <v>46266</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="21" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="12" t="s">
@@ -1640,7 +1739,7 @@
       <c r="F12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="24" t="s">
         <v>117</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -1663,13 +1762,13 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="13">
         <v>46266</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="12" t="s">
@@ -1681,7 +1780,7 @@
       <c r="F13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="24" t="s">
         <v>105</v>
       </c>
       <c r="H13" s="12" t="s">
@@ -1704,7 +1803,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="23" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="13">
@@ -1722,7 +1821,7 @@
       <c r="F14" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="24" t="s">
         <v>119</v>
       </c>
       <c r="H14" s="12" t="s">
@@ -1745,7 +1844,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="23" t="s">
         <v>46</v>
       </c>
       <c r="B15" s="13">
@@ -1763,7 +1862,7 @@
       <c r="F15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="24" t="s">
         <v>105</v>
       </c>
       <c r="H15" s="12" t="s">
@@ -1786,7 +1885,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="23" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="13">
@@ -1804,7 +1903,7 @@
       <c r="F16" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="24" t="s">
         <v>62</v>
       </c>
       <c r="H16" s="12" t="s">
@@ -1827,7 +1926,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="23" t="s">
         <v>68</v>
       </c>
       <c r="B17" s="13">
@@ -1845,7 +1944,7 @@
       <c r="F17" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="24" t="s">
         <v>115</v>
       </c>
       <c r="H17" s="12" t="s">
@@ -1868,7 +1967,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="23" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="13">
@@ -1886,7 +1985,7 @@
       <c r="F18" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="24" t="s">
         <v>111</v>
       </c>
       <c r="H18" s="12" t="s">
@@ -1909,7 +2008,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="23" t="s">
         <v>75</v>
       </c>
       <c r="B19" s="13">
@@ -1927,7 +2026,7 @@
       <c r="F19" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="24" t="s">
         <v>62</v>
       </c>
       <c r="H19" s="12" t="s">
@@ -1950,7 +2049,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="23" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="13">
@@ -1968,7 +2067,7 @@
       <c r="F20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="24" t="s">
         <v>115</v>
       </c>
       <c r="H20" s="12" t="s">
@@ -1991,7 +2090,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="23" t="s">
         <v>75</v>
       </c>
       <c r="B21" s="13">
@@ -2009,7 +2108,7 @@
       <c r="F21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="24" t="s">
         <v>111</v>
       </c>
       <c r="H21" s="12" t="s">
@@ -2032,7 +2131,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="23" t="s">
         <v>82</v>
       </c>
       <c r="B22" s="13">
@@ -2050,7 +2149,7 @@
       <c r="F22" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="24" t="s">
         <v>104</v>
       </c>
       <c r="H22" s="12" t="s">
@@ -2073,7 +2172,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="23" t="s">
         <v>82</v>
       </c>
       <c r="B23" s="13">
@@ -2091,22 +2190,22 @@
       <c r="F23" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="K23" s="20">
+      <c r="K23" s="19">
         <v>1</v>
       </c>
-      <c r="L23" s="21">
+      <c r="L23" s="20">
         <v>750000</v>
       </c>
       <c r="M23" s="14">
@@ -2122,37 +2221,39 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
@@ -2163,36 +2264,36 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>126</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B8" s="16"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
-        <v>22</v>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>137</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>23</v>
@@ -2200,20 +2301,38 @@
       <c r="C12" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="24" t="s">
+      <c r="D12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="13">
         <v>46266</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="D13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="13">
@@ -2222,9 +2341,18 @@
       <c r="C14" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="D14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="13">
@@ -2233,9 +2361,18 @@
       <c r="C15" s="12" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="D15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
         <v>68</v>
       </c>
       <c r="B16" s="13">
@@ -2244,9 +2381,18 @@
       <c r="C16" s="12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="D16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>75</v>
       </c>
       <c r="B17" s="13">
@@ -2255,9 +2401,18 @@
       <c r="C17" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+      <c r="D17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
         <v>82</v>
       </c>
       <c r="B18" s="13">
@@ -2266,100 +2421,130 @@
       <c r="C18" s="12" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="D18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
-        <v>28</v>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>139</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="35" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
+      <c r="D21" s="35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="24" t="s">
         <v>117</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="37" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+      <c r="D22" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="24" t="s">
         <v>105</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="37" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="D23" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
         <v>119</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="37" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="D24" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="24" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="37" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="D25" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
         <v>111</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="37" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
+      <c r="D26" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24" t="s">
         <v>115</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="37" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="D27" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="27" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>28</v>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>128</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>32</v>
@@ -2368,11 +2553,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="28" t="s">
         <v>117</v>
       </c>
       <c r="C31" s="12">
@@ -2382,11 +2567,11 @@
         <v>1850000</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="24" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="28" t="s">
         <v>105</v>
       </c>
       <c r="C32" s="12">
@@ -2396,11 +2581,11 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="28" t="s">
         <v>119</v>
       </c>
       <c r="C33" s="12">
@@ -2409,12 +2594,13 @@
       <c r="D33" s="14">
         <v>750000</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+      <c r="K33" s="19"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="28" t="s">
         <v>105</v>
       </c>
       <c r="C34" s="12">
@@ -2424,11 +2610,11 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="28" t="s">
         <v>62</v>
       </c>
       <c r="C35" s="12">
@@ -2438,11 +2624,11 @@
         <v>350000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="28" t="s">
         <v>115</v>
       </c>
       <c r="C36" s="12">
@@ -2452,11 +2638,11 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="28" t="s">
         <v>111</v>
       </c>
       <c r="C37" s="12">
@@ -2466,11 +2652,11 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="28" t="s">
         <v>62</v>
       </c>
       <c r="C38" s="12">
@@ -2480,11 +2666,11 @@
         <v>375000</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="28" t="s">
         <v>115</v>
       </c>
       <c r="C39" s="12">
@@ -2494,11 +2680,11 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="28" t="s">
         <v>111</v>
       </c>
       <c r="C40" s="12">
@@ -2508,8 +2694,8 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="28" t="s">
         <v>82</v>
       </c>
       <c r="B41" s="29" t="s">
@@ -2522,17 +2708,17 @@
         <v>1850000</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="19">
         <v>1</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="20">
         <v>750000</v>
       </c>
     </row>
@@ -2544,65 +2730,590 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="16" t="s">
+        <v>131</v>
+      </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="16" t="s">
+        <v>132</v>
+      </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="31"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="35" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="38"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="38"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="27" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="12">
+        <v>1</v>
+      </c>
+      <c r="D48" s="14">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="12">
+        <v>2</v>
+      </c>
+      <c r="D49" s="14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="12">
+        <v>1</v>
+      </c>
+      <c r="D50" s="14">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="12">
+        <v>1</v>
+      </c>
+      <c r="D51" s="14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" s="12">
+        <v>3</v>
+      </c>
+      <c r="D52" s="14">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C53" s="12">
+        <v>10</v>
+      </c>
+      <c r="D53" s="14">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="12">
+        <v>2</v>
+      </c>
+      <c r="D54" s="14">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="12">
+        <v>1</v>
+      </c>
+      <c r="D55" s="14">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" s="12">
+        <v>5</v>
+      </c>
+      <c r="D56" s="14">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="12">
+        <v>1</v>
+      </c>
+      <c r="D57" s="14">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B58" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="12">
+        <v>2</v>
+      </c>
+      <c r="D58" s="14">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="19">
+        <v>1</v>
+      </c>
+      <c r="D59" s="20">
+        <v>750000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Normalisasi_SalesDB_Muhammad Fariz.xlsx
+++ b/Normalisasi_SalesDB_Muhammad Fariz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Maganghub\Bootcamp\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0769C4A1-1646-44DB-A27E-7F50B141E337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED0AFAB1-CEDF-4D30-9932-B80C8ADC19FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,21 @@
     <sheet name="2_1NF" sheetId="3" r:id="rId3"/>
     <sheet name="3_2NF" sheetId="4" r:id="rId4"/>
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
+    <sheet name="ERD" sheetId="6" r:id="rId6"/>
+    <sheet name="SQL" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -72,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="212">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -534,6 +547,5850 @@
   </si>
   <si>
     <t>Kode Produk (PK)</t>
+  </si>
+  <si>
+    <r>
+      <t>IF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>EXISTS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF00FF00"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>sys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF00FF00"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>databases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'SalesDB'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BEGIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATABASE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> SalesDB</t>
+    </r>
+  </si>
+  <si>
+    <t>END</t>
+  </si>
+  <si>
+    <t>GO</t>
+  </si>
+  <si>
+    <r>
+      <t>USE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> SalesDB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Email </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        City </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+  </si>
+  <si>
+    <t>)</t>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NONCLUSTERED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INDEX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UQ_Employee_Email</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Email </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        OrderID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Order </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEWID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CustomerID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DATETIME2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> DF_Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SYSDATETIME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_Order_Customer </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        SubCategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_Category_SubCategory </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SubCategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>IDENTITY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_Product </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>KEY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        CategoryID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        UnitPrice </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Stock </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_Product_Category </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> OrderDetail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        OrderID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>UNIQUEIDENTIFIER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        ProductID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        Qty </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CK_OrderDetail_Qty </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">CHECK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">Qty </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PK_OrderDetail </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>PRIMARY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_OrderDetail_Order </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> [Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONSTRAINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> FK_OrderDetail_Product </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>FOREIGN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KEY </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>REFERENCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> City</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Budi Santoso'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'budi@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Jakarta'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Siti Aminah'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'siti@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Bandung'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Andi Wijaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'andi@mail.com'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Surbaya'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>SubCategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Elektronik'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Alat Tulis'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(NULL,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Aksesoris Komputer'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>[Order]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CustomerID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'AF045C04-91E1-40E0-9C83-D73323EE65D4'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-01'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'DE66E0FF-4162-4D24-B877-12B837DCE58F'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-10'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'BBAB2B35-EB6E-4B3C-9DD7-C56485324953'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-12'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'AF045C04-91E1-40E0-9C83-D73323EE65D4'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-15'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'DE66E0FF-4162-4D24-B877-12B837DCE58F'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-18'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'BBAB2B35-EB6E-4B3C-9DD7-C56485324953'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'2026-09-20'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF00FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>CategoryID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Stock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Monitor 24 inci'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Mouse Wireless'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Keyboard Mekanik'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Headset USB'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 375000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Pulpen Gel (isi 12)'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>N'Buku Catatan A5'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>INSERT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>INTO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> dbo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderDetail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>OrderID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> ProductID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Qty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> UnitPrice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">VALUES  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'B893A8B1-F1A8-4101-96ED-41B12434E946'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'B893A8B1-F1A8-4101-96ED-41B12434E946'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'D7251C90-3135-4163-826C-E0D068479095'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'D7251C90-3135-4163-826C-E0D068479095'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 150000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'8E4A0FA5-F2D1-4870-AAB4-C108E3D0220D'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 350000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'FEB6D622-5F34-4B87-A32B-77EC13428A6F'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'FEB6D622-5F34-4B87-A32B-77EC13428A6F'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'CCF36378-A64A-4BED-9931-3D2787B77F38'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 375000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'CCF36378-A64A-4BED-9931-3D2787B77F38'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 25000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'CCF36378-A64A-4BED-9931-3D2787B77F38'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 48000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'44B32496-8DCE-471E-8A89-E7B0E0CFB49F'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1850000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>'44B32496-8DCE-471E-8A89-E7B0E0CFB49F'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> 750000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Cascadia Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -543,7 +6400,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -640,6 +6497,42 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00FF00"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="13">
@@ -749,7 +6642,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -835,6 +6728,18 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -850,6 +6755,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB63AD13-79BB-7AE6-3F53-22A36E2EF6D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="771525"/>
+          <a:ext cx="9544050" cy="3257550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2730,36 +8690,37 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
@@ -2770,7 +8731,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
@@ -2781,7 +8742,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
@@ -2789,17 +8750,17 @@
         <v>133</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>137</v>
       </c>
@@ -2809,11 +8770,8 @@
       <c r="C12" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
         <v>35</v>
       </c>
@@ -2823,11 +8781,8 @@
       <c r="C13" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
         <v>46</v>
       </c>
@@ -2837,11 +8792,8 @@
       <c r="C14" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
         <v>57</v>
       </c>
@@ -2851,11 +8803,8 @@
       <c r="C15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
         <v>68</v>
       </c>
@@ -2864,9 +8813,6 @@
       </c>
       <c r="C16" s="12" t="s">
         <v>36</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2879,9 +8825,6 @@
       <c r="C17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="18" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
@@ -2892,9 +8835,6 @@
       </c>
       <c r="C18" s="12" t="s">
         <v>58</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2918,6 +8858,9 @@
       <c r="C21" s="11" t="s">
         <v>26</v>
       </c>
+      <c r="D21" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
@@ -2929,6 +8872,9 @@
       <c r="C22" s="12" t="s">
         <v>38</v>
       </c>
+      <c r="D22" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
@@ -2940,6 +8886,9 @@
       <c r="C23" s="12" t="s">
         <v>49</v>
       </c>
+      <c r="D23" s="12" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
@@ -2951,371 +8900,809 @@
       <c r="C24" s="12" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>38</v>
+      <c r="D24" s="12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>49</v>
+      <c r="A26" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="33" t="s">
-        <v>58</v>
+      <c r="A27" s="24" t="s">
+        <v>117</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>60</v>
+        <v>118</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>135</v>
+      <c r="A29" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="C30" s="37" t="s">
         <v>64</v>
       </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>109</v>
+        <v>113</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="38"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="38"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="27" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="12">
+        <v>1</v>
+      </c>
+      <c r="D42" s="14">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="12">
+        <v>2</v>
+      </c>
+      <c r="D43" s="14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
+      <c r="C44" s="12">
+        <v>1</v>
+      </c>
+      <c r="D44" s="14">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="12">
+        <v>1</v>
+      </c>
+      <c r="D45" s="14">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
+      <c r="C46" s="12">
+        <v>3</v>
+      </c>
+      <c r="D46" s="14">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="38"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="B38" s="35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="27" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>33</v>
+      <c r="C47" s="12">
+        <v>10</v>
+      </c>
+      <c r="D47" s="14">
+        <v>25000</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="28" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="B48" s="28" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C48" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="14">
-        <v>1850000</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="28" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="C49" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" s="14">
-        <v>150000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="B50" s="28" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C50" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D50" s="14">
-        <v>750000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="28" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C51" s="12">
         <v>1</v>
       </c>
       <c r="D51" s="14">
-        <v>150000</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>62</v>
+        <v>82</v>
+      </c>
+      <c r="B52" s="29" t="s">
+        <v>117</v>
       </c>
       <c r="C52" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52" s="14">
-        <v>350000</v>
+        <v>1850000</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C53" s="12">
-        <v>10</v>
-      </c>
-      <c r="D53" s="14">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C54" s="12">
-        <v>2</v>
-      </c>
-      <c r="D54" s="14">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C55" s="12">
+        <v>82</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="19">
         <v>1</v>
       </c>
-      <c r="D55" s="14">
-        <v>375000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" s="12">
-        <v>5</v>
-      </c>
-      <c r="D56" s="14">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="B57" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57" s="12">
-        <v>1</v>
-      </c>
-      <c r="D57" s="14">
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="B58" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="C58" s="12">
-        <v>2</v>
-      </c>
-      <c r="D58" s="14">
-        <v>1850000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="B59" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C59" s="19">
-        <v>1</v>
-      </c>
-      <c r="D59" s="20">
+      <c r="D53" s="20">
         <v>750000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC714E5D-1476-462F-BE82-9344D71EB8F3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A341BD09-2DC5-46D8-AA94-4AFC3AA4A74E}">
+  <dimension ref="A1:A98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="41"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="41"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="41"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="40" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="40" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="42" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="41"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="40" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="40" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="41"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="41"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="42" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="41"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="39" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="41"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="40" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="42" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="41"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="39" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="40" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="40" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="41"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="40" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="42" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="41"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="39" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="40" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="41"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="40" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="40" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="40" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="42" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="41"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="39" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="41"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="39" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="41"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="39" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="41"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="39" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="39" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="39" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="39" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="41"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="39" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="39" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="39" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="39" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="41"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="39" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="39" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="39" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="39" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="39" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="39" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="39" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="39" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="39" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="39" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="39" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Normalisasi_SalesDB_Muhammad Fariz.xlsx
+++ b/Normalisasi_SalesDB_Muhammad Fariz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Maganghub\Bootcamp\Latihan-database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EB5307-3E78-4699-BA0E-0C3E1BFCA6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C502F3-9C9F-430A-A063-E492CE2F1ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="287">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -10899,6 +10899,21 @@
       </rPr>
       <t>00</t>
     </r>
+  </si>
+  <si>
+    <t>---Gagal karena ada constraint untuk menjaga qty barang saat di beli harus besar dari 0</t>
+  </si>
+  <si>
+    <t>---Gagal karena untuk CustemerID tipe datanya adalah GUID</t>
+  </si>
+  <si>
+    <t>---Gagal karena ada constrain check agar stock pada produk harus besar sama dari 0</t>
+  </si>
+  <si>
+    <t>---Berhasil karena kolom Email pada tabel Customer memperbolehkan NULL</t>
+  </si>
+  <si>
+    <t>---Gagal karena ada constraint pada kolom email harus bernilai unique tetapi tidak termasuk nilai NULL</t>
   </si>
 </sst>
 </file>
@@ -13765,7 +13780,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A341BD09-2DC5-46D8-AA94-4AFC3AA4A74E}">
-  <dimension ref="A1:A246"/>
+  <dimension ref="A1:A256"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -14693,109 +14708,107 @@
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="43" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="41"/>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="43" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" s="39" t="s">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="39" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A202" s="40" t="s">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="40" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A203" s="40" t="s">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="40" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A204" s="39" t="s">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="39" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A205" s="41"/>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A206" s="40" t="s">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="41"/>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="40" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A207" s="40" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A208" s="41"/>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="41"/>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A211" s="43" t="s">
+      <c r="A211" s="40" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="41"/>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="43" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="41"/>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="43" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A212" s="39" t="s">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="39" t="s">
         <v>229</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A213" s="40" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A214" s="40" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A215" s="40" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A216" s="40" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" s="40" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A218" s="39" t="s">
-        <v>255</v>
+      <c r="A218" s="40" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A219" s="41"/>
+      <c r="A219" s="40" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" s="40" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" s="40" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A222" s="40" t="s">
-        <v>258</v>
+      <c r="A222" s="39" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.25">
@@ -14803,105 +14816,147 @@
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" s="40" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A225" s="41"/>
+      <c r="A225" s="40" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A226" s="43" t="s">
-        <v>271</v>
+      <c r="A226" s="40" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A227" s="39" t="s">
-        <v>229</v>
-      </c>
+      <c r="A227" s="41"/>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A228" s="40" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A229" s="40" t="s">
-        <v>273</v>
-      </c>
+      <c r="A229" s="41"/>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A230" s="39" t="s">
-        <v>274</v>
+      <c r="A230" s="43" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" s="41"/>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A232" s="42" t="s">
-        <v>275</v>
+      <c r="A232" s="43" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A233" s="41"/>
+      <c r="A233" s="39" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" s="40" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="40" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="39" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="41"/>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="42" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="41"/>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="40" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A235" s="41"/>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A236" s="43" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A237" s="39" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A238" s="40" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A239" s="40" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A240" s="39" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A241" s="41"/>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A242" s="40" t="s">
-        <v>279</v>
+      <c r="A242" s="43" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A243" s="40" t="s">
-        <v>280</v>
-      </c>
+      <c r="A243" s="41"/>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A244" s="40" t="s">
-        <v>258</v>
+      <c r="A244" s="43" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A245" s="41"/>
+      <c r="A245" s="39" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A246" s="40" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="40" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="39" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="41"/>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="40" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="40" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="41"/>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="40" t="s">
         <v>281</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="41"/>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="43" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
